--- a/app/tmp/reporte_ovejas.xlsx
+++ b/app/tmp/reporte_ovejas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,20 +16,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
-  </numFmts>
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,22 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,172 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Fecha de Nacimiento</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Raza</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Sexo</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ID Padre</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>ID Madre</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>raquel</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>45557</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>dorper</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Macho</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>leyla</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>45563</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>dorper</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Hembra</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>45563</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>dorper</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Macho</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>gemela</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>45564</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>dorper</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Hembra</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>leylaa</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>45564</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>dorperll</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Hembra</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>